--- a/templates/HEM4_Facility_List_Options_ICF.xlsx
+++ b/templates/HEM4_Facility_List_Options_ICF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\39492\Desktop\202007114_Tier1_tool_output_files_fix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55586\Desktop\tools\access tool\access-tool-migration\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA11308C-9EA0-451A-A34C-D091167A2192}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404135E2-63F3-48F7-888D-BBEBCA384D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7305" yWindow="2700" windowWidth="26265" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility List Options" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="MS Sans Serif"/>
@@ -459,6 +459,11 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="MS Sans Serif"/>
     </font>
@@ -540,14 +545,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -560,16 +561,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,9 +697,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -735,9 +737,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -770,26 +772,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -822,26 +807,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1119,203 +1087,176 @@
   <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" customWidth="1"/>
-    <col min="12" max="12" width="51.7109375" customWidth="1"/>
-    <col min="13" max="13" width="6.5703125" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" customWidth="1"/>
-    <col min="17" max="17" width="5.140625" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" customWidth="1"/>
-    <col min="21" max="21" width="6" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" customWidth="1"/>
-    <col min="23" max="23" width="5.85546875" customWidth="1"/>
-    <col min="24" max="24" width="10" customWidth="1"/>
-    <col min="25" max="26" width="9.140625" customWidth="1"/>
-    <col min="27" max="27" width="11.42578125" customWidth="1"/>
-    <col min="29" max="29" width="14" customWidth="1"/>
-    <col min="30" max="30" width="13.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="51.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="6.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="5.140625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="5.28515625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="5.85546875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="6" style="2" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="5.85546875" style="2" customWidth="1"/>
+    <col min="24" max="24" width="10" style="2" customWidth="1"/>
+    <col min="25" max="26" width="9.140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" style="2" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="2"/>
+    <col min="29" max="29" width="14" style="2" customWidth="1"/>
+    <col min="30" max="30" width="13.85546875" style="2" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:30" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11" t="s">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="9" t="s">
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="12" t="s">
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="X1" s="13"/>
-      <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="13"/>
-      <c r="AD1" s="13"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
     </row>
-    <row r="2" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Y2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="Z2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AA2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AB2" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AC2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AD2" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
+    <row r="3" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1355,15 +1296,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="c8c52b2b-e099-45be-aa49-d42c893f956d" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="c8c52b2b-e099-45be-aa49-d42c893f956d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A6418311839E004E863CB303EF7712E8" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f1c8763dd603a2ce8eb294d237e894f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0050cb40-2a8d-4839-9389-7f464a6eeb3e" xmlns:ns4="c8c52b2b-e099-45be-aa49-d42c893f956d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="888a553cc08695bd68bb89a17972725a" ns3:_="" ns4:_="">
     <xsd:import namespace="0050cb40-2a8d-4839-9389-7f464a6eeb3e"/>
@@ -1598,6 +1530,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="c8c52b2b-e099-45be-aa49-d42c893f956d" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="c8c52b2b-e099-45be-aa49-d42c893f956d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5731BC23-D422-4B88-B24B-F5A43BF31BB7}">
   <ds:schemaRefs>
@@ -1607,23 +1548,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD2788B-6FAA-47FD-B49C-E484634ABEC0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c8c52b2b-e099-45be-aa49-d42c893f956d"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="0050cb40-2a8d-4839-9389-7f464a6eeb3e"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{124186FE-25AD-4578-ADFD-BB3E484CAD08}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1640,4 +1564,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAD2788B-6FAA-47FD-B49C-E484634ABEC0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="c8c52b2b-e099-45be-aa49-d42c893f956d"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="0050cb40-2a8d-4839-9389-7f464a6eeb3e"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/templates/HEM4_Facility_List_Options_ICF.xlsx
+++ b/templates/HEM4_Facility_List_Options_ICF.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55586\Desktop\tools\access tool\access-tool-migration\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{404135E2-63F3-48F7-888D-BBEBCA384D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139E717A-1903-4C3A-B4CF-6A8F1F48E0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7305" yWindow="2700" windowWidth="26265" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6465" yWindow="2130" windowWidth="26265" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facility List Options" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="MS Sans Serif"/>
@@ -444,14 +444,6 @@
       <sz val="10"/>
       <name val="MS Sans Serif"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -465,7 +457,10 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="MS Sans Serif"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -543,35 +538,39 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1087,176 +1086,205 @@
   <dimension ref="A1:AD3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="5.5703125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="51.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="6.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="5.140625" style="2" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="6.7109375" style="2" customWidth="1"/>
-    <col min="21" max="21" width="6" style="2" customWidth="1"/>
-    <col min="22" max="22" width="6.5703125" style="2" customWidth="1"/>
-    <col min="23" max="23" width="5.85546875" style="2" customWidth="1"/>
-    <col min="24" max="24" width="10" style="2" customWidth="1"/>
-    <col min="25" max="26" width="9.140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="11.42578125" style="2" customWidth="1"/>
-    <col min="28" max="28" width="9.140625" style="2"/>
-    <col min="29" max="29" width="14" style="2" customWidth="1"/>
-    <col min="30" max="30" width="13.85546875" style="2" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="18.85546875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="15" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" style="15" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="9" style="15" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="15" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" style="15" customWidth="1"/>
+    <col min="11" max="11" width="27.5703125" style="15" customWidth="1"/>
+    <col min="12" max="12" width="51.7109375" style="15" customWidth="1"/>
+    <col min="13" max="13" width="6.5703125" style="15" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" style="15" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="15" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="15" customWidth="1"/>
+    <col min="17" max="17" width="5.140625" style="15" customWidth="1"/>
+    <col min="18" max="18" width="5.28515625" style="15" customWidth="1"/>
+    <col min="19" max="19" width="5.85546875" style="15" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="15" customWidth="1"/>
+    <col min="21" max="21" width="6" style="15" customWidth="1"/>
+    <col min="22" max="22" width="6.5703125" style="15" customWidth="1"/>
+    <col min="23" max="23" width="5.85546875" style="15" customWidth="1"/>
+    <col min="24" max="24" width="10" style="15" customWidth="1"/>
+    <col min="25" max="26" width="9.140625" style="15" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" style="15" customWidth="1"/>
+    <col min="28" max="28" width="9.140625" style="15"/>
+    <col min="29" max="29" width="14" style="15" customWidth="1"/>
+    <col min="30" max="30" width="13.85546875" style="15" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="6" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="7" t="s">
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="5" t="s">
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="8" t="s">
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
     </row>
-    <row r="2" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="10" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="10" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="10" t="s">
+      <c r="V2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="10" t="s">
+      <c r="W2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="X2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="10" t="s">
+      <c r="Y2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="10" t="s">
+      <c r="Z2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="10" t="s">
+      <c r="AA2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AB2" s="10" t="s">
+      <c r="AB2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" s="10" t="s">
+      <c r="AC2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" s="10" t="s">
+      <c r="AD2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
+    <row r="3" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
